--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486703_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486703_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6046</v>
+        <v>4.6186</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0415</v>
+        <v>4.8004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5631</v>
+        <v>-0.1818</v>
       </c>
       <c r="G2" t="n">
         <v>4.1468</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7514</v>
+        <v>1.7654</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9854</v>
+        <v>0.7443</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7661</v>
+        <v>1.0211</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3282</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8066</v>
+        <v>4.5542</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5854</v>
+        <v>2.482</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2212</v>
+        <v>2.0722</v>
       </c>
       <c r="G3" t="n">
         <v>3.5293</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7559</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0273</v>
+        <v>-0.0761</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7286</v>
+        <v>0.5796</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8545</v>
+        <v>2.4295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5507</v>
+        <v>1.2746</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3038</v>
+        <v>1.1549</v>
       </c>
       <c r="G4" t="n">
         <v>0.7081</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0113</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7725</v>
+        <v>-0.0486</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.6348</v>
       </c>
       <c r="V4" t="n">
         <v>0.9421</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.368</v>
+        <v>1.7031</v>
       </c>
       <c r="E5" t="n">
-        <v>2.362</v>
+        <v>2.6723</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.994</v>
+        <v>-0.9692</v>
       </c>
       <c r="G5" t="n">
         <v>0.1096</v>
@@ -844,13 +844,13 @@
         <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0385</v>
+        <v>0.2966</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.607</v>
+        <v>-0.2967</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5685</v>
+        <v>0.5933</v>
       </c>
       <c r="V5" t="n">
         <v>2.4554</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3378</v>
+        <v>1.6647</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4643</v>
+        <v>0.5678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8734</v>
+        <v>1.0969</v>
       </c>
       <c r="G6" t="n">
         <v>1.6703</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3971</v>
+        <v>0.724</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0279</v>
+        <v>0.0755</v>
       </c>
       <c r="U6" t="n">
-        <v>0.425</v>
+        <v>0.6485</v>
       </c>
       <c r="V6" t="n">
         <v>0.0426</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8907</v>
+        <v>0.5572</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1026</v>
+        <v>2.8232</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2118</v>
+        <v>-2.2661</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3225</v>
+        <v>1.8429</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2073</v>
+        <v>0.1993</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5298</v>
+        <v>1.6435</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5097</v>
+        <v>4.1682</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4486</v>
+        <v>2.1313</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0611</v>
+        <v>2.0369</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1871</v>
+        <v>-2.3253</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6558</v>
+        <v>-1.9319</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5313</v>
+        <v>-0.3934</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5336</v>
+        <v>0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7168</v>
+        <v>-0.1865</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8168</v>
+        <v>0.4141</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6138</v>
+        <v>-1.5133</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6138</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6109</v>
+        <v>0.3777</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9267</v>
+        <v>1.6889</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3157</v>
+        <v>-1.3112</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8429</v>
+        <v>1.3225</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1993</v>
+        <v>-1.2073</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6435</v>
+        <v>2.5298</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1682</v>
+        <v>3.5097</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1313</v>
+        <v>0.4486</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0369</v>
+        <v>3.0611</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3253</v>
+        <v>-2.1871</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9319</v>
+        <v>-1.6558</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3934</v>
+        <v>-0.5313</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2814</v>
+        <v>1.0206</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.3031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3644</v>
+        <v>0.7175</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5133</v>
+        <v>-0.6138</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5133</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4177</v>
+        <v>-0.0402</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1211</v>
+        <v>-1.846</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5387999999999999</v>
+        <v>1.8058</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2604</v>
+        <v>-0.5713</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.283</v>
+        <v>0.7377</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0226</v>
+        <v>-1.3089</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9286</v>
+        <v>-0.1839</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2134</v>
+        <v>0.4626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2848</v>
+        <v>-0.6465</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3318</v>
+        <v>-0.3874</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0695</v>
+        <v>0.275</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2623</v>
+        <v>-0.6624</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2867</v>
+        <v>-0.0482</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1928</v>
+        <v>-0.3106</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0939</v>
+        <v>0.2624</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1698</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9298</v>
+        <v>-0.0701</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3631</v>
+        <v>0.1211</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4333</v>
+        <v>-0.1912</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5713</v>
+        <v>-3.2604</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7377</v>
+        <v>-3.283</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3089</v>
+        <v>0.0226</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1839</v>
+        <v>-0.9286</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4626</v>
+        <v>-1.2134</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6465</v>
+        <v>0.2848</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3874</v>
+        <v>-2.3318</v>
       </c>
       <c r="N10" t="n">
-        <v>0.275</v>
+        <v>-2.0695</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6624</v>
+        <v>-0.2623</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9378</v>
+        <v>0.6344</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8277</v>
+        <v>0.1928</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1101</v>
+        <v>0.4415</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.1698</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5915</v>
+        <v>-1.2605</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0528</v>
+        <v>-2.8459</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4613</v>
+        <v>1.5855</v>
       </c>
       <c r="G11" t="n">
         <v>-1.015</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2482</v>
+        <v>0.0828</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3588</v>
+        <v>0.483</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3282</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.5341</v>
+        <v>14.5342</v>
       </c>
       <c r="E12" t="n">
         <v>11.7384</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7958</v>
+        <v>2.795800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>8.482799999999999</v>
@@ -1360,7 +1360,7 @@
         <v>4.481199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0015</v>
+        <v>4.001499999999999</v>
       </c>
       <c r="J12" t="n">
         <v>22.4239</v>
@@ -1390,13 +1390,13 @@
         <v>11.5847</v>
       </c>
       <c r="S12" t="n">
-        <v>5.7929</v>
+        <v>5.792899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.002899999999999792</v>
+        <v>-0.003000000000000114</v>
       </c>
       <c r="U12" t="n">
-        <v>5.7958</v>
+        <v>5.795799999999999</v>
       </c>
       <c r="V12" t="n">
         <v>3.1546</v>
@@ -1405,7 +1405,7 @@
         <v>3.7982</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6437000000000002</v>
+        <v>-0.6437000000000004</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9686</v>
+        <v>1.8085</v>
       </c>
       <c r="E13" t="n">
-        <v>3.932</v>
+        <v>4.4491</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9634</v>
+        <v>-2.6406</v>
       </c>
       <c r="G13" t="n">
         <v>6.5173</v>
@@ -1468,13 +1468,13 @@
         <v>2.8962</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2675</v>
+        <v>-1.4276</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7935</v>
+        <v>-1.2764</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.474</v>
+        <v>-0.1512</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3505</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0907</v>
+        <v>-0.276</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5375</v>
+        <v>-0.0897</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4468</v>
+        <v>-0.1863</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1323</v>
+        <v>-0.3174</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1238</v>
+        <v>-0.0483</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2562</v>
+        <v>-0.269</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9454</v>
+        <v>0.0207</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4698</v>
+        <v>0.0207</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5244</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0777</v>
+        <v>-0.3381</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3459</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7318</v>
+        <v>-0.269</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9308</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8962</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9328</v>
+        <v>0.0414</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.104</v>
+        <v>-0.1104</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0368</v>
+        <v>0.1518</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8219</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4135</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2015</v>
+        <v>-0.4944</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0897</v>
+        <v>0.2646</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1118</v>
+        <v>-0.759</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3174</v>
+        <v>-0.6212</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0483</v>
+        <v>0.2898</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.269</v>
+        <v>-0.911</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0207</v>
+        <v>0.3999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0207</v>
+        <v>1.0487</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6488</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3381</v>
+        <v>-1.0211</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.7588</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.269</v>
+        <v>-0.2623</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1159</v>
+        <v>0.262</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1104</v>
+        <v>0.193</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2262</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2048</v>
+        <v>-1.0897</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6783</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8831</v>
+        <v>-0.4046</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6212</v>
+        <v>-4.5418</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2898</v>
+        <v>-2.7377</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.911</v>
+        <v>-1.8041</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3999</v>
+        <v>-0.3951</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0487</v>
+        <v>0.091</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6488</v>
+        <v>-0.486</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0211</v>
+        <v>-4.1467</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7588</v>
+        <v>-2.8287</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2623</v>
+        <v>-1.3181</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>2.7031</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1931</v>
+        <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5515</v>
+        <v>-1.6688</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6066</v>
+        <v>-1.5177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0551</v>
+        <v>-0.1512</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>2.4178</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3282</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-1.235</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2462</v>
+        <v>-0.6553</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5189</v>
+        <v>-0.5797</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.16</v>
+        <v>-1.366</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7508</v>
+        <v>-1.6758</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4092</v>
+        <v>0.3097</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.6208</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.164</v>
+        <v>-1.1927</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5674</v>
+        <v>0.572</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4286</v>
+        <v>-0.7453</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5868</v>
+        <v>-0.483</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1582</v>
+        <v>-0.2623</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7377</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7031</v>
+        <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1823</v>
+        <v>-0.0621</v>
       </c>
       <c r="T17" t="n">
-        <v>0.165</v>
+        <v>-0.0346</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3472</v>
+        <v>-0.0275</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3779</v>
+        <v>-1.2486</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2383</v>
+        <v>-1.8667</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1396</v>
+        <v>0.6182</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4662</v>
+        <v>-2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4413</v>
+        <v>-1.7508</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0249</v>
+        <v>-0.4092</v>
       </c>
       <c r="J18" t="n">
-        <v>0.003</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6481</v>
+        <v>-0.164</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6511</v>
+        <v>-0.5674</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4692</v>
+        <v>-1.4286</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2068</v>
+        <v>-1.5868</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.1582</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3862</v>
+        <v>2.7031</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2097</v>
+        <v>-0.7035</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2759</v>
+        <v>-0.4556</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2479</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1228</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1228</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4874</v>
+        <v>-1.2786</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7588</v>
+        <v>-1.2383</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7287</v>
+        <v>-0.0402</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.366</v>
+        <v>-0.4662</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6758</v>
+        <v>-0.4413</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3097</v>
+        <v>-0.0249</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6208</v>
+        <v>0.003</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1927</v>
+        <v>-0.6481</v>
       </c>
       <c r="L19" t="n">
-        <v>0.572</v>
+        <v>0.6511</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7453</v>
+        <v>-0.4692</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.483</v>
+        <v>0.2068</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2623</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3145</v>
+        <v>-0.1104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.138</v>
+        <v>-0.2759</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1765</v>
+        <v>0.1655</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5779</v>
+        <v>-1.3819</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0987</v>
+        <v>-0.5375</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4791</v>
+        <v>-0.8444</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.5418</v>
+        <v>-2.1323</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7377</v>
+        <v>0.1238</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8041</v>
+        <v>-2.2562</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3951</v>
+        <v>1.9454</v>
       </c>
       <c r="K20" t="n">
-        <v>0.091</v>
+        <v>2.4698</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.486</v>
+        <v>-0.5244</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1467</v>
+        <v>-4.0777</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.8287</v>
+        <v>-2.3459</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3181</v>
+        <v>-1.7318</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7031</v>
+        <v>1.9308</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7031</v>
+        <v>2.8962</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.157</v>
+        <v>-0.3585</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.9314</v>
+        <v>-1.104</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2257</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4178</v>
+        <v>-0.8219</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>-0.4135</v>
       </c>
       <c r="X20" t="n">
-        <v>1.1902</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0542</v>
+        <v>-1.7562</v>
       </c>
       <c r="E21" t="n">
         <v>0.1032</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1574</v>
+        <v>-1.8594</v>
       </c>
       <c r="G21" t="n">
         <v>1.5596</v>
@@ -2092,13 +2092,13 @@
         <v>2.51</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0152</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3866</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6286</v>
+        <v>-0.3306</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2124</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5189</v>
+        <v>-2.3947</v>
       </c>
       <c r="E22" t="n">
         <v>0.0471</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.566</v>
+        <v>-2.4418</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7465</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7724</v>
+        <v>-0.6482</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4415</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3309</v>
+        <v>-0.2068</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2621</v>
+        <v>-5.1876</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5872</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6749</v>
+        <v>-2.6004</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2083</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4745</v>
+        <v>-0.4</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.5341</v>
+        <v>-14.5342</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7958</v>
+        <v>-2.795700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.7383</v>
+        <v>-11.7382</v>
       </c>
       <c r="G24" t="n">
         <v>-8.482800000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.481300000000001</v>
+        <v>-4.481299999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-4.001500000000001</v>
@@ -2305,7 +2305,7 @@
         <v>9.3179</v>
       </c>
       <c r="L24" t="n">
-        <v>4.6235</v>
+        <v>4.623499999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-22.424</v>
@@ -2317,7 +2317,7 @@
         <v>-8.625</v>
       </c>
       <c r="P24" t="n">
-        <v>2.8962</v>
+        <v>2.896199999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.5848</v>
@@ -2332,7 +2332,7 @@
         <v>-5.795999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.002999999999999892</v>
+        <v>0.00289999999999992</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1546</v>
